--- a/data/output/2025/evaluasi_52.xlsx
+++ b/data/output/2025/evaluasi_52.xlsx
@@ -17,6 +17,7 @@
     <sheet name="5208" sheetId="8" state="visible" r:id="rId8"/>
     <sheet name="5271" sheetId="9" state="visible" r:id="rId9"/>
     <sheet name="5272" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet name="5202" sheetId="11" state="visible" r:id="rId11"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -928,7 +929,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F2"/>
+  <dimension ref="A1:F11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -988,6 +989,444 @@
       <c r="F2" t="inlineStr">
         <is>
           <t>Nilai revisi lebih dari (+-4 point) dari nilai rilis</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>5272</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Kota Bima</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>7.049424728452839</v>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>q-to-q_pklnprt_q4-25_prov vs q-to-q_pklnprt_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>5272</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Kota Bima</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>44.53396767657764</v>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>q-to-q_pkp_q4-25_prov vs q-to-q_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>5272</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Kota Bima</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>5.688148537178406</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>q-to-q_pmtb_q4-25_prov vs q-to-q_pmtb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>5272</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Kota Bima</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>6.13520978143579</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>y-on-y_pdrb_q4-25_prov vs y-on-y_pdrb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>5272</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Kota Bima</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>16.08462235191905</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>y-on-y_pkp_q4-25_prov vs y-on-y_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>5272</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Kota Bima</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>6.52518564296413</v>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>y-on-y_pmtb_q4-25_prov vs y-on-y_pmtb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>5272</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Kota Bima</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>-5.318658613149585</v>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>c-to-c_pklnprt_q4-25_prov vs c-to-c_pklnprt_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>5272</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Kota Bima</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>13.94164793591064</v>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>c-to-c_pkp_q4-25_prov vs c-to-c_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>5272</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Kota Bima</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>6.346418007923662</v>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>c-to-c_pmtb_q4-25_prov vs c-to-c_pmtb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F6"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>kode</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>kabupaten/kota</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>periode</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>nilai</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>kolom</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>evaluasi</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>5202</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Kabupaten Lombok Tengah</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D2" t="n">
+        <v>7.864951844577142</v>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>q-to-q_pklnprt_q4-25_prov vs q-to-q_pklnprt_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>5202</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Kabupaten Lombok Tengah</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>58.41899831576145</v>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>q-to-q_pkp_q4-25_prov vs q-to-q_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>5202</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Kabupaten Lombok Tengah</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>4.869063647406318</v>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>y-on-y_pdrb_q4-25_prov vs y-on-y_pdrb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>5202</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Kabupaten Lombok Tengah</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>24.39163384930806</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>y-on-y_pkp_q4-25_prov vs y-on-y_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>5202</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Kabupaten Lombok Tengah</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>10.74745368680612</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>c-to-c_pkp_q4-25_prov vs c-to-c_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
         </is>
       </c>
     </row>
@@ -1002,7 +1441,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F2"/>
+  <dimension ref="A1:F8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1062,6 +1501,174 @@
       <c r="F2" t="inlineStr">
         <is>
           <t>Nilai revisi lebih dari (+-4 point) dari nilai rilis</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>5201</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Kabupaten Lombok Barat</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>5.950000000000143</v>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>q-to-q_pklnprt_q4-25_prov vs q-to-q_pklnprt_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>5201</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Kabupaten Lombok Barat</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>45.50391657161387</v>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>q-to-q_pkp_q4-25_prov vs q-to-q_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>5201</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Kabupaten Lombok Barat</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>5.019633014331271</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>y-on-y_pdrb_q4-25_prov vs y-on-y_pdrb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>5201</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Kabupaten Lombok Barat</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>15.05068075553501</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>y-on-y_pkp_q4-25_prov vs y-on-y_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>5201</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Kabupaten Lombok Barat</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>7.611395067103596</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>c-to-c_pkp_q4-25_prov vs c-to-c_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>5201</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Kabupaten Lombok Barat</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>5.529441510431239</v>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>implisit_y-on-y_pmtb_2025_prov vs implisit_y-on-y_pmtb_2025_kab</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
         </is>
       </c>
     </row>
@@ -1076,7 +1683,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F2"/>
+  <dimension ref="A1:F6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1136,6 +1743,118 @@
       <c r="F2" t="inlineStr">
         <is>
           <t>Nilai revisi lebih dari (+-4 point) dari nilai rilis</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>5203</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Kabupaten Lombok Timur</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>7.03831567787982</v>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>q-to-q_pklnprt_q4-25_prov vs q-to-q_pklnprt_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>5203</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Kabupaten Lombok Timur</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>40.88043975905738</v>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>q-to-q_pkp_q4-25_prov vs q-to-q_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>5203</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Kabupaten Lombok Timur</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>5.644996321759697</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>y-on-y_pdrb_q4-25_prov vs y-on-y_pdrb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>5203</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Kabupaten Lombok Timur</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>14.17384145476834</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>y-on-y_pkp_q4-25_prov vs y-on-y_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
         </is>
       </c>
     </row>
@@ -1150,7 +1869,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F3"/>
+  <dimension ref="A1:F8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1238,6 +1957,146 @@
       <c r="F3" t="inlineStr">
         <is>
           <t>SoG PI lebih dari +-2 persen</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>5204</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Kabupaten Sumbawa</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>9.217467582345975</v>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>q-to-q_pklnprt_q4-25_prov vs q-to-q_pklnprt_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>5204</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Kabupaten Sumbawa</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>68.87558988469374</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>q-to-q_pkp_q4-25_prov vs q-to-q_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>5204</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Kabupaten Sumbawa</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>6.420133842197679</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>y-on-y_pdrb_q4-25_prov vs y-on-y_pdrb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>5204</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Kabupaten Sumbawa</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>22.47311503817207</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>y-on-y_pkp_q4-25_prov vs y-on-y_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>5204</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Kabupaten Sumbawa</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>6.649983878441337</v>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>implisit_y-on-y_pmtb_q4-25_prov vs implisit_y-on-y_pmtb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
         </is>
       </c>
     </row>
@@ -1252,7 +2111,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F5"/>
+  <dimension ref="A1:F12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1396,6 +2255,202 @@
       <c r="F5" t="inlineStr">
         <is>
           <t>SoG PI lebih dari +-2 persen</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>5205</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Kabupaten Dompu</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>10.3743939987892</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>q-to-q_pklnprt_q4-25_prov vs q-to-q_pklnprt_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>5205</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Kabupaten Dompu</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>21.42657401790012</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>q-to-q_pkp_q4-25_prov vs q-to-q_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>5205</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Kabupaten Dompu</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>5.076571427206082</v>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>q-to-q_pmtb_q4-25_prov vs q-to-q_pmtb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>5205</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Kabupaten Dompu</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>4.981696161151214</v>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>y-on-y_pdrb_q4-25_prov vs y-on-y_pdrb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>5205</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Kabupaten Dompu</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>-0.2222787765892727</v>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>y-on-y_pkp_q4-25_prov vs y-on-y_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>5205</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Kabupaten Dompu</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>-0.4695482383135847</v>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>c-to-c_pkp_q4-25_prov vs c-to-c_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>5205</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Kabupaten Dompu</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>0.1174317854019888</v>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>implisit_y-on-y_pkp_q4-25_prov vs implisit_y-on-y_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
         </is>
       </c>
     </row>
@@ -1410,7 +2465,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F3"/>
+  <dimension ref="A1:F8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1498,6 +2553,146 @@
       <c r="F3" t="inlineStr">
         <is>
           <t>SoG PI lebih dari +-2 persen</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>5206</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Kabupaten Bima</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>3.747187724068434</v>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>q-to-q_pklnprt_q4-25_prov vs q-to-q_pklnprt_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>5206</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Kabupaten Bima</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>29.71768786728052</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>q-to-q_pkp_q4-25_prov vs q-to-q_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>5206</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Kabupaten Bima</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>6.068084295409777</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>y-on-y_pdrb_q4-25_prov vs y-on-y_pdrb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>5206</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Kabupaten Bima</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>9.103513398785806</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>y-on-y_pkp_q4-25_prov vs y-on-y_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>5206</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Kabupaten Bima</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>6.257585595069119</v>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>implisit_y-on-y_pkp_2025_prov vs implisit_y-on-y_pkp_2025_kab</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
         </is>
       </c>
     </row>
@@ -1512,7 +2707,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F2"/>
+  <dimension ref="A1:F9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1572,6 +2767,202 @@
       <c r="F2" t="inlineStr">
         <is>
           <t>Nilai revisi lebih dari (+-4 point) dari nilai rilis</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>5207</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Kabupaten Sumbawa Barat</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>6.831120430129532</v>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>q-to-q_pklnprt_q4-25_prov vs q-to-q_pklnprt_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>5207</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Kabupaten Sumbawa Barat</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>36.55974893760047</v>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>q-to-q_pkp_q4-25_prov vs q-to-q_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>5207</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Kabupaten Sumbawa Barat</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>5.686731940101464</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>q-to-q_pmtb_q4-25_prov vs q-to-q_pmtb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>5207</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Kabupaten Sumbawa Barat</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>5.874269802233536</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>y-on-y_pdrb_q4-25_prov vs y-on-y_pdrb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>5207</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Kabupaten Sumbawa Barat</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>10.33082876823334</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>y-on-y_pkp_q4-25_prov vs y-on-y_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>5207</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Kabupaten Sumbawa Barat</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>-3.777906741849272</v>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>c-to-c_pklnprt_q4-25_prov vs c-to-c_pklnprt_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>5207</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Kabupaten Sumbawa Barat</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>6.108137133845389</v>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>c-to-c_pmtb_q4-25_prov vs c-to-c_pmtb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
         </is>
       </c>
     </row>
@@ -1586,7 +2977,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F2"/>
+  <dimension ref="A1:F7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1646,6 +3037,146 @@
       <c r="F2" t="inlineStr">
         <is>
           <t>Nilai revisi lebih dari (+-4 point) dari nilai rilis</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>5208</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Kabupaten Lombok Utara</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>5.942759931319514</v>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>q-to-q_pklnprt_q4-25_prov vs q-to-q_pklnprt_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>5208</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Kabupaten Lombok Utara</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>39.7351808783869</v>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>q-to-q_pkp_q4-25_prov vs q-to-q_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>5208</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Kabupaten Lombok Utara</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>5.227039913015111</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>y-on-y_pdrb_q4-25_prov vs y-on-y_pdrb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>5208</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Kabupaten Lombok Utara</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>-5.205617378663923</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>c-to-c_pklnprt_q4-25_prov vs c-to-c_pklnprt_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>5208</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Kabupaten Lombok Utara</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>-3.977101589001202</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>c-to-c_pkp_q4-25_prov vs c-to-c_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
         </is>
       </c>
     </row>
@@ -1660,7 +3191,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F2"/>
+  <dimension ref="A1:F8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1723,6 +3254,174 @@
         </is>
       </c>
     </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>5271</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Kota Mataram</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>5.52724511893777</v>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>q-to-q_pklnprt_q4-25_prov vs q-to-q_pklnprt_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>5271</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Kota Mataram</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>38.8233357435867</v>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>q-to-q_pkp_q4-25_prov vs q-to-q_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>5271</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Kota Mataram</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>6.397847107615896</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>q-to-q_pmtb_q4-25_prov vs q-to-q_pmtb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>5271</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Kota Mataram</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>5.410749801496239</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>y-on-y_pdrb_q4-25_prov vs y-on-y_pdrb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>5271</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Kota Mataram</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>28.61881765036974</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>y-on-y_pkp_q4-25_prov vs y-on-y_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>5271</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Kota Mataram</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>-3.437552440679306</v>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>c-to-c_pklnprt_q4-25_prov vs c-to-c_pklnprt_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
